--- a/CPDS-AD_dataset/scenario_records/FDI_attacks/local_model_consistent/test_data_LMC_4/data_three_phase_meter_2.xlsx
+++ b/CPDS-AD_dataset/scenario_records/FDI_attacks/local_model_consistent/test_data_LMC_4/data_three_phase_meter_2.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:01.960</t>
+          <t>2026/6/30 00:00:01.960</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -531,7 +531,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:06.605</t>
+          <t>2026/6/30 00:00:06.605</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -571,7 +571,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:11.300</t>
+          <t>2026/6/30 00:00:11.300</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -611,7 +611,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:16.897</t>
+          <t>2026/6/30 00:00:16.897</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:21.529</t>
+          <t>2026/6/30 00:00:21.529</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -691,7 +691,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:26.215</t>
+          <t>2026/6/30 00:00:26.215</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:30.861</t>
+          <t>2026/6/30 00:00:30.861</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -771,7 +771,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:35.836</t>
+          <t>2026/6/30 00:00:35.836</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:40.834</t>
+          <t>2026/6/30 00:00:40.834</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -851,7 +851,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:45.463</t>
+          <t>2026/6/30 00:00:45.463</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:50.160</t>
+          <t>2026/6/30 00:00:50.160</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -931,7 +931,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:56.027</t>
+          <t>2026/6/30 00:00:56.027</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -971,7 +971,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:00.700</t>
+          <t>2026/6/30 00:01:00.700</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:05.368</t>
+          <t>2026/6/30 00:01:05.368</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:10.053</t>
+          <t>2026/6/30 00:01:10.053</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:15.309</t>
+          <t>2026/6/30 00:01:15.309</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:20.312</t>
+          <t>2026/6/30 00:01:20.312</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:24.932</t>
+          <t>2026/6/30 00:01:24.932</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:29.601</t>
+          <t>2026/6/30 00:01:29.601</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:34.567</t>
+          <t>2026/6/30 00:01:34.567</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:39.874</t>
+          <t>2026/6/30 00:01:39.874</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:44.544</t>
+          <t>2026/6/30 00:01:44.544</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:49.212</t>
+          <t>2026/6/30 00:01:49.212</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:54.768</t>
+          <t>2026/6/30 00:01:54.768</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:59.786</t>
+          <t>2026/6/30 00:01:59.786</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:04.432</t>
+          <t>2026/6/30 00:02:04.432</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:09.130</t>
+          <t>2026/6/30 00:02:09.130</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:14.050</t>
+          <t>2026/6/30 00:02:14.050</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:19.354</t>
+          <t>2026/6/30 00:02:19.354</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:24.029</t>
+          <t>2026/6/30 00:02:24.029</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:28.657</t>
+          <t>2026/6/30 00:02:28.657</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:33.659</t>
+          <t>2026/6/30 00:02:33.659</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:38.968</t>
+          <t>2026/6/30 00:02:38.968</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:43.573</t>
+          <t>2026/6/30 00:02:43.573</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:53.241</t>
+          <t>2026/6/30 00:02:53.241</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:53.241</t>
+          <t>2026/6/30 00:02:53.241</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:58.801</t>
+          <t>2026/6/30 00:02:58.801</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:03.511</t>
+          <t>2026/6/30 00:03:03.511</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:13.128</t>
+          <t>2026/6/30 00:03:13.128</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:18.132</t>
+          <t>2026/6/30 00:03:18.132</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:22.756</t>
+          <t>2026/6/30 00:03:22.756</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:27.405</t>
+          <t>2026/6/30 00:03:27.405</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:32.108</t>
+          <t>2026/6/30 00:03:32.108</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:37.692</t>
+          <t>2026/6/30 00:03:37.692</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:42.361</t>
+          <t>2026/6/30 00:03:42.361</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:47.035</t>
+          <t>2026/6/30 00:03:47.035</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:51.676</t>
+          <t>2026/6/30 00:03:51.676</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:57.606</t>
+          <t>2026/6/30 00:03:57.606</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:02.271</t>
+          <t>2026/6/30 00:04:02.271</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:06.904</t>
+          <t>2026/6/30 00:04:06.904</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:11.597</t>
+          <t>2026/6/30 00:04:11.597</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:16.235</t>
+          <t>2026/6/30 00:04:16.235</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:21.231</t>
+          <t>2026/6/30 00:04:21.231</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:25.886</t>
+          <t>2026/6/30 00:04:25.886</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:30.558</t>
+          <t>2026/6/30 00:04:30.558</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:35.821</t>
+          <t>2026/6/30 00:04:35.821</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:40.803</t>
+          <t>2026/6/30 00:04:40.803</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:45.425</t>
+          <t>2026/6/30 00:04:45.425</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:50.098</t>
+          <t>2026/6/30 00:04:50.098</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:56.032</t>
+          <t>2026/6/30 00:04:56.032</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:00.666</t>
+          <t>2026/6/30 00:05:00.666</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:05.989</t>
+          <t>2026/6/30 00:05:05.989</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:10.668</t>
+          <t>2026/6/30 00:05:10.668</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:15.936</t>
+          <t>2026/6/30 00:05:15.936</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:20.914</t>
+          <t>2026/6/30 00:05:20.914</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:25.564</t>
+          <t>2026/6/30 00:05:25.564</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:30.214</t>
+          <t>2026/6/30 00:05:30.214</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:35.499</t>
+          <t>2026/6/30 00:05:35.499</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:40.503</t>
+          <t>2026/6/30 00:05:40.503</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:45.140</t>
+          <t>2026/6/30 00:05:45.140</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:49.807</t>
+          <t>2026/6/30 00:05:49.807</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:55.424</t>
+          <t>2026/6/30 00:05:55.424</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:00.354</t>
+          <t>2026/6/30 00:06:00.354</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:05.050</t>
+          <t>2026/6/30 00:06:05.050</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:09.697</t>
+          <t>2026/6/30 00:06:09.697</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:15.018</t>
+          <t>2026/6/30 00:06:15.018</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:19.967</t>
+          <t>2026/6/30 00:06:19.967</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:24.616</t>
+          <t>2026/6/30 00:06:24.616</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:29.302</t>
+          <t>2026/6/30 00:06:29.302</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:34.242</t>
+          <t>2026/6/30 00:06:34.242</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:39.540</t>
+          <t>2026/6/30 00:06:39.540</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:44.232</t>
+          <t>2026/6/30 00:06:44.232</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:48.895</t>
+          <t>2026/6/30 00:06:48.895</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:54.144</t>
+          <t>2026/6/30 00:06:54.144</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:59.427</t>
+          <t>2026/6/30 00:06:59.427</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:04.412</t>
+          <t>2026/6/30 00:07:04.412</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:09.069</t>
+          <t>2026/6/30 00:07:09.069</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:14.058</t>
+          <t>2026/6/30 00:07:14.058</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:19.327</t>
+          <t>2026/6/30 00:07:19.327</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:23.996</t>
+          <t>2026/6/30 00:07:23.996</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:28.689</t>
+          <t>2026/6/30 00:07:28.689</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:33.662</t>
+          <t>2026/6/30 00:07:33.662</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:38.922</t>
+          <t>2026/6/30 00:07:38.922</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:43.578</t>
+          <t>2026/6/30 00:07:43.578</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:52.918</t>
+          <t>2026/6/30 00:07:52.918</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:57.600</t>
+          <t>2026/6/30 00:07:57.600</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:02.243</t>
+          <t>2026/6/30 00:08:02.243</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:06.881</t>
+          <t>2026/6/30 00:08:06.881</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:11.592</t>
+          <t>2026/6/30 00:08:11.592</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:17.176</t>
+          <t>2026/6/30 00:08:17.176</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:21.838</t>
+          <t>2026/6/30 00:08:21.838</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:26.496</t>
+          <t>2026/6/30 00:08:26.496</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:31.165</t>
+          <t>2026/6/30 00:08:31.165</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:36.472</t>
+          <t>2026/6/30 00:08:36.472</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:41.407</t>
+          <t>2026/6/30 00:08:41.407</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:46.102</t>
+          <t>2026/6/30 00:08:46.102</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:50.731</t>
+          <t>2026/6/30 00:08:50.731</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:56.641</t>
+          <t>2026/6/30 00:08:56.641</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:01.289</t>
+          <t>2026/6/30 00:09:01.289</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:05.999</t>
+          <t>2026/6/30 00:09:05.999</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:10.618</t>
+          <t>2026/6/30 00:09:10.618</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:15.932</t>
+          <t>2026/6/30 00:09:15.932</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:20.888</t>
+          <t>2026/6/30 00:09:20.888</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:25.554</t>
+          <t>2026/6/30 00:09:25.554</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:30.208</t>
+          <t>2026/6/30 00:09:30.208</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:35.519</t>
+          <t>2026/6/30 00:09:35.519</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:40.459</t>
+          <t>2026/6/30 00:09:40.459</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:45.156</t>
+          <t>2026/6/30 00:09:45.156</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:49.787</t>
+          <t>2026/6/30 00:09:49.787</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:55.378</t>
+          <t>2026/6/30 00:09:55.378</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:00.342</t>
+          <t>2026/6/30 00:10:00.342</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:05.030</t>
+          <t>2026/6/30 00:10:05.030</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:09.717</t>
+          <t>2026/6/30 00:10:09.717</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:14.978</t>
+          <t>2026/6/30 00:10:14.978</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:19.939</t>
+          <t>2026/6/30 00:10:19.939</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:24.631</t>
+          <t>2026/6/30 00:10:24.631</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:29.268</t>
+          <t>2026/6/30 00:10:29.268</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:34.251</t>
+          <t>2026/6/30 00:10:34.251</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:39.535</t>
+          <t>2026/6/30 00:10:39.535</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:44.214</t>
+          <t>2026/6/30 00:10:44.214</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:48.836</t>
+          <t>2026/6/30 00:10:48.836</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:54.122</t>
+          <t>2026/6/30 00:10:54.122</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:59.411</t>
+          <t>2026/6/30 00:10:59.411</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:04.111</t>
+          <t>2026/6/30 00:11:04.111</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:08.753</t>
+          <t>2026/6/30 00:11:08.753</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:13.758</t>
+          <t>2026/6/30 00:11:13.758</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:19.003</t>
+          <t>2026/6/30 00:11:19.003</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:23.679</t>
+          <t>2026/6/30 00:11:23.679</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:33.287</t>
+          <t>2026/6/30 00:11:33.287</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:37.996</t>
+          <t>2026/6/30 00:11:37.996</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:42.649</t>
+          <t>2026/6/30 00:11:42.649</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:47.313</t>
+          <t>2026/6/30 00:11:47.313</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:51.977</t>
+          <t>2026/6/30 00:11:51.977</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:57.892</t>
+          <t>2026/6/30 00:11:57.892</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:02.526</t>
+          <t>2026/6/30 00:12:02.526</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:07.219</t>
+          <t>2026/6/30 00:12:07.219</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:11.868</t>
+          <t>2026/6/30 00:12:11.868</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:17.478</t>
+          <t>2026/6/30 00:12:17.478</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:22.129</t>
+          <t>2026/6/30 00:12:22.129</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:26.806</t>
+          <t>2026/6/30 00:12:26.806</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:31.478</t>
+          <t>2026/6/30 00:12:31.478</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:36.748</t>
+          <t>2026/6/30 00:12:36.748</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:41.409</t>
+          <t>2026/6/30 00:12:41.409</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:46.061</t>
+          <t>2026/6/30 00:12:46.061</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:50.734</t>
+          <t>2026/6/30 00:12:50.734</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:56.620</t>
+          <t>2026/6/30 00:12:56.620</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:01.286</t>
+          <t>2026/6/30 00:13:01.286</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:05.989</t>
+          <t>2026/6/30 00:13:05.989</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:10.621</t>
+          <t>2026/6/30 00:13:10.621</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:15.878</t>
+          <t>2026/6/30 00:13:15.878</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:20.878</t>
+          <t>2026/6/30 00:13:20.878</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:25.545</t>
+          <t>2026/6/30 00:13:25.545</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:30.209</t>
+          <t>2026/6/30 00:13:30.209</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:35.500</t>
+          <t>2026/6/30 00:13:35.500</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:40.444</t>
+          <t>2026/6/30 00:13:40.444</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:45.134</t>
+          <t>2026/6/30 00:13:45.134</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:49.778</t>
+          <t>2026/6/30 00:13:49.778</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:55.411</t>
+          <t>2026/6/30 00:13:55.411</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:00.379</t>
+          <t>2026/6/30 00:14:00.379</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:05.024</t>
+          <t>2026/6/30 00:14:05.024</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:09.662</t>
+          <t>2026/6/30 00:14:09.662</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:14.952</t>
+          <t>2026/6/30 00:14:14.952</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:19.960</t>
+          <t>2026/6/30 00:14:19.960</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:24.619</t>
+          <t>2026/6/30 00:14:24.619</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:29.267</t>
+          <t>2026/6/30 00:14:29.267</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:34.265</t>
+          <t>2026/6/30 00:14:34.265</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:39.539</t>
+          <t>2026/6/30 00:14:39.539</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:44.194</t>
+          <t>2026/6/30 00:14:44.194</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:48.823</t>
+          <t>2026/6/30 00:14:48.823</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:54.168</t>
+          <t>2026/6/30 00:14:54.168</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:59.393</t>
+          <t>2026/6/30 00:14:59.393</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:04.095</t>
+          <t>2026/6/30 00:15:04.095</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:08.769</t>
+          <t>2026/6/30 00:15:08.769</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:13.712</t>
+          <t>2026/6/30 00:15:13.712</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:18.705</t>
+          <t>2026/6/30 00:15:18.705</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:28.010</t>
+          <t>2026/6/30 00:15:28.010</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:32.676</t>
+          <t>2026/6/30 00:15:32.676</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:38.298</t>
+          <t>2026/6/30 00:15:38.298</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:42.928</t>
+          <t>2026/6/30 00:15:42.928</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:47.580</t>
+          <t>2026/6/30 00:15:47.580</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:52.286</t>
+          <t>2026/6/30 00:15:52.286</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:58.174</t>
+          <t>2026/6/30 00:15:58.174</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:02.837</t>
+          <t>2026/6/30 00:16:02.837</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:07.486</t>
+          <t>2026/6/30 00:16:07.486</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:12.159</t>
+          <t>2026/6/30 00:16:12.159</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:17.109</t>
+          <t>2026/6/30 00:16:17.109</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:21.775</t>
+          <t>2026/6/30 00:16:21.775</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:26.472</t>
+          <t>2026/6/30 00:16:26.472</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:31.096</t>
+          <t>2026/6/30 00:16:31.096</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:36.386</t>
+          <t>2026/6/30 00:16:36.386</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:41.383</t>
+          <t>2026/6/30 00:16:41.383</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:46.036</t>
+          <t>2026/6/30 00:16:46.036</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:50.699</t>
+          <t>2026/6/30 00:16:50.699</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:56.578</t>
+          <t>2026/6/30 00:16:56.578</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:01.263</t>
+          <t>2026/6/30 00:17:01.263</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:05.927</t>
+          <t>2026/6/30 00:17:05.927</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:10.609</t>
+          <t>2026/6/30 00:17:10.609</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:15.887</t>
+          <t>2026/6/30 00:17:15.887</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:20.833</t>
+          <t>2026/6/30 00:17:20.833</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:25.494</t>
+          <t>2026/6/30 00:17:25.494</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:30.171</t>
+          <t>2026/6/30 00:17:30.171</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:35.469</t>
+          <t>2026/6/30 00:17:35.469</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:40.438</t>
+          <t>2026/6/30 00:17:40.438</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:45.132</t>
+          <t>2026/6/30 00:17:45.132</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:49.734</t>
+          <t>2026/6/30 00:17:49.734</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:55.359</t>
+          <t>2026/6/30 00:17:55.359</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:00.356</t>
+          <t>2026/6/30 00:18:00.356</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:05.008</t>
+          <t>2026/6/30 00:18:05.008</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:09.647</t>
+          <t>2026/6/30 00:18:09.647</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -9251,7 +9251,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:14.637</t>
+          <t>2026/6/30 00:18:14.637</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:19.924</t>
+          <t>2026/6/30 00:18:19.924</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:24.567</t>
+          <t>2026/6/30 00:18:24.567</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:29.251</t>
+          <t>2026/6/30 00:18:29.251</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:34.250</t>
+          <t>2026/6/30 00:18:34.250</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:39.516</t>
+          <t>2026/6/30 00:18:39.516</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:44.185</t>
+          <t>2026/6/30 00:18:44.185</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:48.812</t>
+          <t>2026/6/30 00:18:48.812</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:54.084</t>
+          <t>2026/6/30 00:18:54.084</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:59.387</t>
+          <t>2026/6/30 00:18:59.387</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:04.078</t>
+          <t>2026/6/30 00:19:04.078</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:08.709</t>
+          <t>2026/6/30 00:19:08.709</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:13.661</t>
+          <t>2026/6/30 00:19:13.661</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:18.983</t>
+          <t>2026/6/30 00:19:18.983</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:23.663</t>
+          <t>2026/6/30 00:19:23.663</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -9851,7 +9851,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:33.300</t>
+          <t>2026/6/30 00:19:33.300</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:38.568</t>
+          <t>2026/6/30 00:19:38.568</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:43.211</t>
+          <t>2026/6/30 00:19:43.211</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -9971,7 +9971,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:47.889</t>
+          <t>2026/6/30 00:19:47.889</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -10011,7 +10011,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:52.577</t>
+          <t>2026/6/30 00:19:52.577</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:57.551</t>
+          <t>2026/6/30 00:19:57.551</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:02.533</t>
+          <t>2026/6/30 00:20:02.533</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:07.171</t>
+          <t>2026/6/30 00:20:07.171</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:11.825</t>
+          <t>2026/6/30 00:20:11.825</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:17.442</t>
+          <t>2026/6/30 00:20:17.442</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:22.087</t>
+          <t>2026/6/30 00:20:22.087</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:26.717</t>
+          <t>2026/6/30 00:20:26.717</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:31.390</t>
+          <t>2026/6/30 00:20:31.390</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -10371,7 +10371,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:36.673</t>
+          <t>2026/6/30 00:20:36.673</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:41.667</t>
+          <t>2026/6/30 00:20:41.667</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -10451,7 +10451,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:46.338</t>
+          <t>2026/6/30 00:20:46.338</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:50.989</t>
+          <t>2026/6/30 00:20:50.989</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:56.601</t>
+          <t>2026/6/30 00:20:56.601</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:01.272</t>
+          <t>2026/6/30 00:21:01.272</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:05.909</t>
+          <t>2026/6/30 00:21:05.909</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:10.573</t>
+          <t>2026/6/30 00:21:10.573</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:15.837</t>
+          <t>2026/6/30 00:21:15.837</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:20.849</t>
+          <t>2026/6/30 00:21:20.849</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:25.482</t>
+          <t>2026/6/30 00:21:25.482</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -10811,7 +10811,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:30.159</t>
+          <t>2026/6/30 00:21:30.159</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:35.439</t>
+          <t>2026/6/30 00:21:35.439</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:40.413</t>
+          <t>2026/6/30 00:21:40.413</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -10931,7 +10931,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:45.078</t>
+          <t>2026/6/30 00:21:45.078</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -10971,7 +10971,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:49.752</t>
+          <t>2026/6/30 00:21:49.752</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:55.323</t>
+          <t>2026/6/30 00:21:55.323</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:00.294</t>
+          <t>2026/6/30 00:22:00.294</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:04.961</t>
+          <t>2026/6/30 00:22:04.961</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:09.615</t>
+          <t>2026/6/30 00:22:09.615</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:14.616</t>
+          <t>2026/6/30 00:22:14.616</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:19.881</t>
+          <t>2026/6/30 00:22:19.881</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:24.558</t>
+          <t>2026/6/30 00:22:24.558</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:29.211</t>
+          <t>2026/6/30 00:22:29.211</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -11331,7 +11331,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:34.181</t>
+          <t>2026/6/30 00:22:34.181</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:39.482</t>
+          <t>2026/6/30 00:22:39.482</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:44.122</t>
+          <t>2026/6/30 00:22:44.122</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:48.819</t>
+          <t>2026/6/30 00:22:48.819</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:54.092</t>
+          <t>2026/6/30 00:22:54.092</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:59.363</t>
+          <t>2026/6/30 00:22:59.363</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:04.064</t>
+          <t>2026/6/30 00:23:04.064</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -11611,7 +11611,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:08.726</t>
+          <t>2026/6/30 00:23:08.726</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:13.658</t>
+          <t>2026/6/30 00:23:13.658</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:18.997</t>
+          <t>2026/6/30 00:23:18.997</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:28.318</t>
+          <t>2026/6/30 00:23:28.318</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:33.265</t>
+          <t>2026/6/30 00:23:33.265</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -11811,7 +11811,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:38.244</t>
+          <t>2026/6/30 00:23:38.244</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -11851,7 +11851,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:43.208</t>
+          <t>2026/6/30 00:23:43.208</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:47.872</t>
+          <t>2026/6/30 00:23:47.872</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:52.832</t>
+          <t>2026/6/30 00:23:52.832</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -11971,7 +11971,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:58.459</t>
+          <t>2026/6/30 00:23:58.459</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -12011,7 +12011,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:03.117</t>
+          <t>2026/6/30 00:24:03.117</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:07.776</t>
+          <t>2026/6/30 00:24:07.776</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:12.435</t>
+          <t>2026/6/30 00:24:12.435</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:18.003</t>
+          <t>2026/6/30 00:24:18.003</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -12171,7 +12171,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:22.686</t>
+          <t>2026/6/30 00:24:22.686</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:27.366</t>
+          <t>2026/6/30 00:24:27.366</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -12251,7 +12251,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:32.046</t>
+          <t>2026/6/30 00:24:32.046</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:37.001</t>
+          <t>2026/6/30 00:24:37.001</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:41.640</t>
+          <t>2026/6/30 00:24:41.640</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:46.336</t>
+          <t>2026/6/30 00:24:46.336</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -12411,7 +12411,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:50.000</t>
+          <t>2026/6/30 00:24:50.000</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:56.884</t>
+          <t>2026/6/30 00:24:56.884</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:01.576</t>
+          <t>2026/6/30 00:25:01.576</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:06.207</t>
+          <t>2026/6/30 00:25:06.207</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -12571,7 +12571,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:10.868</t>
+          <t>2026/6/30 00:25:10.868</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -12611,7 +12611,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:16.145</t>
+          <t>2026/6/30 00:25:16.145</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:21.122</t>
+          <t>2026/6/30 00:25:21.122</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:25.801</t>
+          <t>2026/6/30 00:25:25.801</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -12731,7 +12731,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:30.484</t>
+          <t>2026/6/30 00:25:30.484</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -12771,7 +12771,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:35.745</t>
+          <t>2026/6/30 00:25:35.745</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -12811,7 +12811,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:40.726</t>
+          <t>2026/6/30 00:25:40.726</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:45.376</t>
+          <t>2026/6/30 00:25:45.376</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -12891,7 +12891,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:50.043</t>
+          <t>2026/6/30 00:25:50.043</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:55.948</t>
+          <t>2026/6/30 00:25:55.948</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -12971,7 +12971,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:00.613</t>
+          <t>2026/6/30 00:26:00.613</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:05.292</t>
+          <t>2026/6/30 00:26:05.292</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -13051,7 +13051,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:09.963</t>
+          <t>2026/6/30 00:26:09.963</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:15.212</t>
+          <t>2026/6/30 00:26:15.212</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -13131,7 +13131,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:20.203</t>
+          <t>2026/6/30 00:26:20.203</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -13171,7 +13171,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:24.852</t>
+          <t>2026/6/30 00:26:24.852</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:29.529</t>
+          <t>2026/6/30 00:26:29.529</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:34.807</t>
+          <t>2026/6/30 00:26:34.807</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -13291,7 +13291,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:39.776</t>
+          <t>2026/6/30 00:26:39.776</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -13331,7 +13331,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:44.445</t>
+          <t>2026/6/30 00:26:44.445</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -13371,7 +13371,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:49.123</t>
+          <t>2026/6/30 00:26:49.123</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -13411,7 +13411,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:54.411</t>
+          <t>2026/6/30 00:26:54.411</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:59.693</t>
+          <t>2026/6/30 00:26:59.693</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:04.336</t>
+          <t>2026/6/30 00:27:04.336</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -13531,7 +13531,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:08.999</t>
+          <t>2026/6/30 00:27:08.999</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -13571,7 +13571,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:13.969</t>
+          <t>2026/6/30 00:27:13.969</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -13611,7 +13611,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:19.285</t>
+          <t>2026/6/30 00:27:19.285</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:24.260</t>
+          <t>2026/6/30 00:27:24.260</t>
         </is>
       </c>
       <c r="C331" t="n">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:28.938</t>
+          <t>2026/6/30 00:27:28.938</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -13731,7 +13731,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:33.879</t>
+          <t>2026/6/30 00:27:33.879</t>
         </is>
       </c>
       <c r="C333" t="n">
@@ -13771,7 +13771,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:39.149</t>
+          <t>2026/6/30 00:27:39.149</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -13811,7 +13811,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:43.849</t>
+          <t>2026/6/30 00:27:43.849</t>
         </is>
       </c>
       <c r="C335" t="n">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:48.508</t>
+          <t>2026/6/30 00:27:48.508</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:53.770</t>
+          <t>2026/6/30 00:27:53.770</t>
         </is>
       </c>
       <c r="C337" t="n">
@@ -13931,7 +13931,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:59.057</t>
+          <t>2026/6/30 00:27:59.057</t>
         </is>
       </c>
       <c r="C338" t="n">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:08.385</t>
+          <t>2026/6/30 00:28:08.385</t>
         </is>
       </c>
       <c r="C339" t="n">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:13.046</t>
+          <t>2026/6/30 00:28:13.046</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -14051,7 +14051,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:17.700</t>
+          <t>2026/6/30 00:28:17.700</t>
         </is>
       </c>
       <c r="C341" t="n">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:22.392</t>
+          <t>2026/6/30 00:28:22.392</t>
         </is>
       </c>
       <c r="C342" t="n">
@@ -14131,7 +14131,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:27.010</t>
+          <t>2026/6/30 00:28:27.010</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -14171,7 +14171,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:31.716</t>
+          <t>2026/6/30 00:28:31.716</t>
         </is>
       </c>
       <c r="C344" t="n">
@@ -14211,7 +14211,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:37.295</t>
+          <t>2026/6/30 00:28:37.295</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -14251,7 +14251,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:41.943</t>
+          <t>2026/6/30 00:28:41.943</t>
         </is>
       </c>
       <c r="C346" t="n">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:46.601</t>
+          <t>2026/6/30 00:28:46.601</t>
         </is>
       </c>
       <c r="C347" t="n">
@@ -14331,7 +14331,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:51.293</t>
+          <t>2026/6/30 00:28:51.293</t>
         </is>
       </c>
       <c r="C348" t="n">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:57.209</t>
+          <t>2026/6/30 00:28:57.209</t>
         </is>
       </c>
       <c r="C349" t="n">
@@ -14411,7 +14411,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:01.850</t>
+          <t>2026/6/30 00:29:01.850</t>
         </is>
       </c>
       <c r="C350" t="n">
@@ -14451,7 +14451,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:06.530</t>
+          <t>2026/6/30 00:29:06.530</t>
         </is>
       </c>
       <c r="C351" t="n">
@@ -14491,7 +14491,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:11.177</t>
+          <t>2026/6/30 00:29:11.177</t>
         </is>
       </c>
       <c r="C352" t="n">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:16.475</t>
+          <t>2026/6/30 00:29:16.475</t>
         </is>
       </c>
       <c r="C353" t="n">
@@ -14571,7 +14571,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:21.424</t>
+          <t>2026/6/30 00:29:21.424</t>
         </is>
       </c>
       <c r="C354" t="n">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:26.109</t>
+          <t>2026/6/30 00:29:26.109</t>
         </is>
       </c>
       <c r="C355" t="n">
@@ -14651,7 +14651,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:30.779</t>
+          <t>2026/6/30 00:29:30.779</t>
         </is>
       </c>
       <c r="C356" t="n">
@@ -14691,7 +14691,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:36.075</t>
+          <t>2026/6/30 00:29:36.075</t>
         </is>
       </c>
       <c r="C357" t="n">
@@ -14731,7 +14731,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:41.037</t>
+          <t>2026/6/30 00:29:41.037</t>
         </is>
       </c>
       <c r="C358" t="n">
@@ -14771,7 +14771,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:45.671</t>
+          <t>2026/6/30 00:29:45.671</t>
         </is>
       </c>
       <c r="C359" t="n">
@@ -14811,7 +14811,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:50.340</t>
+          <t>2026/6/30 00:29:50.340</t>
         </is>
       </c>
       <c r="C360" t="n">
@@ -14851,7 +14851,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:56.251</t>
+          <t>2026/6/30 00:29:56.251</t>
         </is>
       </c>
       <c r="C361" t="n">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:00.893</t>
+          <t>2026/6/30 00:30:00.893</t>
         </is>
       </c>
       <c r="C362" t="n">
@@ -14931,7 +14931,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:05.565</t>
+          <t>2026/6/30 00:30:05.565</t>
         </is>
       </c>
       <c r="C363" t="n">
@@ -14971,7 +14971,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:10.243</t>
+          <t>2026/6/30 00:30:10.243</t>
         </is>
       </c>
       <c r="C364" t="n">
@@ -15011,7 +15011,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:15.510</t>
+          <t>2026/6/30 00:30:15.510</t>
         </is>
       </c>
       <c r="C365" t="n">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:20.508</t>
+          <t>2026/6/30 00:30:20.508</t>
         </is>
       </c>
       <c r="C366" t="n">
@@ -15091,7 +15091,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:25.166</t>
+          <t>2026/6/30 00:30:25.166</t>
         </is>
       </c>
       <c r="C367" t="n">
@@ -15131,7 +15131,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:29.835</t>
+          <t>2026/6/30 00:30:29.835</t>
         </is>
       </c>
       <c r="C368" t="n">
@@ -15171,7 +15171,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:35.095</t>
+          <t>2026/6/30 00:30:35.095</t>
         </is>
       </c>
       <c r="C369" t="n">
@@ -15211,7 +15211,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:40.097</t>
+          <t>2026/6/30 00:30:40.097</t>
         </is>
       </c>
       <c r="C370" t="n">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:44.749</t>
+          <t>2026/6/30 00:30:44.749</t>
         </is>
       </c>
       <c r="C371" t="n">
@@ -15291,7 +15291,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:49.383</t>
+          <t>2026/6/30 00:30:49.383</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:54.978</t>
+          <t>2026/6/30 00:30:54.978</t>
         </is>
       </c>
       <c r="C373" t="n">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:59.955</t>
+          <t>2026/6/30 00:30:59.955</t>
         </is>
       </c>
       <c r="C374" t="n">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:04.619</t>
+          <t>2026/6/30 00:31:04.619</t>
         </is>
       </c>
       <c r="C375" t="n">
@@ -15451,7 +15451,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:09.288</t>
+          <t>2026/6/30 00:31:09.288</t>
         </is>
       </c>
       <c r="C376" t="n">
@@ -15491,7 +15491,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:14.264</t>
+          <t>2026/6/30 00:31:14.264</t>
         </is>
       </c>
       <c r="C377" t="n">
@@ -15531,7 +15531,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:19.578</t>
+          <t>2026/6/30 00:31:19.578</t>
         </is>
       </c>
       <c r="C378" t="n">
@@ -15571,7 +15571,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:24.188</t>
+          <t>2026/6/30 00:31:24.188</t>
         </is>
       </c>
       <c r="C379" t="n">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:28.901</t>
+          <t>2026/6/30 00:31:28.901</t>
         </is>
       </c>
       <c r="C380" t="n">
@@ -15651,7 +15651,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:33.864</t>
+          <t>2026/6/30 00:31:33.864</t>
         </is>
       </c>
       <c r="C381" t="n">
@@ -15691,7 +15691,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:39.156</t>
+          <t>2026/6/30 00:31:39.156</t>
         </is>
       </c>
       <c r="C382" t="n">
@@ -15731,7 +15731,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:43.826</t>
+          <t>2026/6/30 00:31:43.826</t>
         </is>
       </c>
       <c r="C383" t="n">
@@ -15771,7 +15771,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:48.464</t>
+          <t>2026/6/30 00:31:48.464</t>
         </is>
       </c>
       <c r="C384" t="n">
@@ -15811,7 +15811,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:53.787</t>
+          <t>2026/6/30 00:31:53.787</t>
         </is>
       </c>
       <c r="C385" t="n">
@@ -15851,7 +15851,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:58.725</t>
+          <t>2026/6/30 00:31:58.725</t>
         </is>
       </c>
       <c r="C386" t="n">
@@ -15891,7 +15891,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:08.359</t>
+          <t>2026/6/30 00:32:08.359</t>
         </is>
       </c>
       <c r="C387" t="n">
@@ -15931,7 +15931,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:13.320</t>
+          <t>2026/6/30 00:32:13.320</t>
         </is>
       </c>
       <c r="C388" t="n">
@@ -15971,7 +15971,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:18.603</t>
+          <t>2026/6/30 00:32:18.603</t>
         </is>
       </c>
       <c r="C389" t="n">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:23.266</t>
+          <t>2026/6/30 00:32:23.266</t>
         </is>
       </c>
       <c r="C390" t="n">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:27.929</t>
+          <t>2026/6/30 00:32:27.929</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -16091,7 +16091,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:32.630</t>
+          <t>2026/6/30 00:32:32.630</t>
         </is>
       </c>
       <c r="C392" t="n">
@@ -16131,7 +16131,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:38.190</t>
+          <t>2026/6/30 00:32:38.190</t>
         </is>
       </c>
       <c r="C393" t="n">
@@ -16171,7 +16171,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:42.837</t>
+          <t>2026/6/30 00:32:42.837</t>
         </is>
       </c>
       <c r="C394" t="n">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:47.522</t>
+          <t>2026/6/30 00:32:47.522</t>
         </is>
       </c>
       <c r="C395" t="n">
@@ -16251,7 +16251,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:52.217</t>
+          <t>2026/6/30 00:32:52.217</t>
         </is>
       </c>
       <c r="C396" t="n">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:57.488</t>
+          <t>2026/6/30 00:32:57.488</t>
         </is>
       </c>
       <c r="C397" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:02.168</t>
+          <t>2026/6/30 00:33:02.168</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:06.798</t>
+          <t>2026/6/30 00:33:06.798</t>
         </is>
       </c>
       <c r="C399" t="n">
@@ -16411,7 +16411,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:11.455</t>
+          <t>2026/6/30 00:33:11.455</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -16451,7 +16451,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:17.065</t>
+          <t>2026/6/30 00:33:17.065</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -16491,7 +16491,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:21.713</t>
+          <t>2026/6/30 00:33:21.713</t>
         </is>
       </c>
       <c r="C402" t="n">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:26.389</t>
+          <t>2026/6/30 00:33:26.389</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -16571,7 +16571,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:31.084</t>
+          <t>2026/6/30 00:33:31.084</t>
         </is>
       </c>
       <c r="C404" t="n">
@@ -16611,7 +16611,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:36.332</t>
+          <t>2026/6/30 00:33:36.332</t>
         </is>
       </c>
       <c r="C405" t="n">
@@ -16651,7 +16651,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:41.290</t>
+          <t>2026/6/30 00:33:41.290</t>
         </is>
       </c>
       <c r="C406" t="n">
@@ -16691,7 +16691,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:45.968</t>
+          <t>2026/6/30 00:33:45.968</t>
         </is>
       </c>
       <c r="C407" t="n">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:50.605</t>
+          <t>2026/6/30 00:33:50.605</t>
         </is>
       </c>
       <c r="C408" t="n">
@@ -16771,7 +16771,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:56.553</t>
+          <t>2026/6/30 00:33:56.553</t>
         </is>
       </c>
       <c r="C409" t="n">
@@ -16811,7 +16811,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:01.177</t>
+          <t>2026/6/30 00:34:01.177</t>
         </is>
       </c>
       <c r="C410" t="n">
@@ -16851,7 +16851,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:05.851</t>
+          <t>2026/6/30 00:34:05.851</t>
         </is>
       </c>
       <c r="C411" t="n">
@@ -16891,7 +16891,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:10.503</t>
+          <t>2026/6/30 00:34:10.503</t>
         </is>
       </c>
       <c r="C412" t="n">
@@ -16931,7 +16931,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:15.831</t>
+          <t>2026/6/30 00:34:15.831</t>
         </is>
       </c>
       <c r="C413" t="n">
@@ -16971,7 +16971,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:20.751</t>
+          <t>2026/6/30 00:34:20.751</t>
         </is>
       </c>
       <c r="C414" t="n">
@@ -17011,7 +17011,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:25.473</t>
+          <t>2026/6/30 00:34:25.473</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -17051,7 +17051,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:30.097</t>
+          <t>2026/6/30 00:34:30.097</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -17091,7 +17091,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:35.402</t>
+          <t>2026/6/30 00:34:35.402</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -17131,7 +17131,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:40.366</t>
+          <t>2026/6/30 00:34:40.366</t>
         </is>
       </c>
       <c r="C418" t="n">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:45.019</t>
+          <t>2026/6/30 00:34:45.019</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -17211,7 +17211,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:49.681</t>
+          <t>2026/6/30 00:34:49.681</t>
         </is>
       </c>
       <c r="C420" t="n">
@@ -17251,7 +17251,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:55.300</t>
+          <t>2026/6/30 00:34:55.300</t>
         </is>
       </c>
       <c r="C421" t="n">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:00.272</t>
+          <t>2026/6/30 00:35:00.272</t>
         </is>
       </c>
       <c r="C422" t="n">
@@ -17331,7 +17331,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:04.938</t>
+          <t>2026/6/30 00:35:04.938</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -17371,7 +17371,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:09.578</t>
+          <t>2026/6/30 00:35:09.578</t>
         </is>
       </c>
       <c r="C424" t="n">
@@ -17411,7 +17411,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:14.568</t>
+          <t>2026/6/30 00:35:14.568</t>
         </is>
       </c>
       <c r="C425" t="n">
@@ -17451,7 +17451,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:19.858</t>
+          <t>2026/6/30 00:35:19.858</t>
         </is>
       </c>
       <c r="C426" t="n">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:24.499</t>
+          <t>2026/6/30 00:35:24.499</t>
         </is>
       </c>
       <c r="C427" t="n">
@@ -17531,7 +17531,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:29.150</t>
+          <t>2026/6/30 00:35:29.150</t>
         </is>
       </c>
       <c r="C428" t="n">
@@ -17571,7 +17571,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:34.112</t>
+          <t>2026/6/30 00:35:34.112</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -17611,7 +17611,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:39.111</t>
+          <t>2026/6/30 00:35:39.111</t>
         </is>
       </c>
       <c r="C430" t="n">
@@ -17651,7 +17651,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:48.453</t>
+          <t>2026/6/30 00:35:48.453</t>
         </is>
       </c>
       <c r="C431" t="n">
@@ -17691,7 +17691,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:53.420</t>
+          <t>2026/6/30 00:35:53.420</t>
         </is>
       </c>
       <c r="C432" t="n">
@@ -17731,7 +17731,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:53.420</t>
+          <t>2026/6/30 00:35:53.420</t>
         </is>
       </c>
       <c r="C433" t="n">
@@ -17771,7 +17771,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:58.996</t>
+          <t>2026/6/30 00:35:58.996</t>
         </is>
       </c>
       <c r="C434" t="n">
@@ -17811,7 +17811,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:08.352</t>
+          <t>2026/6/30 00:36:08.352</t>
         </is>
       </c>
       <c r="C435" t="n">
@@ -17851,7 +17851,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:13.286</t>
+          <t>2026/6/30 00:36:13.286</t>
         </is>
       </c>
       <c r="C436" t="n">
@@ -17891,7 +17891,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:18.587</t>
+          <t>2026/6/30 00:36:18.587</t>
         </is>
       </c>
       <c r="C437" t="n">
@@ -17931,7 +17931,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:23.230</t>
+          <t>2026/6/30 00:36:23.230</t>
         </is>
       </c>
       <c r="C438" t="n">
@@ -17971,7 +17971,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:27.950</t>
+          <t>2026/6/30 00:36:27.950</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -18011,7 +18011,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:32.560</t>
+          <t>2026/6/30 00:36:32.560</t>
         </is>
       </c>
       <c r="C440" t="n">
@@ -18051,7 +18051,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:37.584</t>
+          <t>2026/6/30 00:36:37.584</t>
         </is>
       </c>
       <c r="C441" t="n">
@@ -18091,7 +18091,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:42.225</t>
+          <t>2026/6/30 00:36:42.225</t>
         </is>
       </c>
       <c r="C442" t="n">
@@ -18131,7 +18131,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:46.892</t>
+          <t>2026/6/30 00:36:46.892</t>
         </is>
       </c>
       <c r="C443" t="n">
@@ -18171,7 +18171,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:51.537</t>
+          <t>2026/6/30 00:36:51.537</t>
         </is>
       </c>
       <c r="C444" t="n">
@@ -18211,7 +18211,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:57.453</t>
+          <t>2026/6/30 00:36:57.453</t>
         </is>
       </c>
       <c r="C445" t="n">
@@ -18251,7 +18251,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:02.121</t>
+          <t>2026/6/30 00:37:02.121</t>
         </is>
       </c>
       <c r="C446" t="n">
@@ -18291,7 +18291,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:06.773</t>
+          <t>2026/6/30 00:37:06.773</t>
         </is>
       </c>
       <c r="C447" t="n">
@@ -18331,7 +18331,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:11.465</t>
+          <t>2026/6/30 00:37:11.465</t>
         </is>
       </c>
       <c r="C448" t="n">
@@ -18371,7 +18371,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:17.018</t>
+          <t>2026/6/30 00:37:17.018</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -18411,7 +18411,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:21.678</t>
+          <t>2026/6/30 00:37:21.678</t>
         </is>
       </c>
       <c r="C450" t="n">
@@ -18451,7 +18451,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:26.370</t>
+          <t>2026/6/30 00:37:26.370</t>
         </is>
       </c>
       <c r="C451" t="n">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:30.998</t>
+          <t>2026/6/30 00:37:30.998</t>
         </is>
       </c>
       <c r="C452" t="n">
@@ -18531,7 +18531,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:36.302</t>
+          <t>2026/6/30 00:37:36.302</t>
         </is>
       </c>
       <c r="C453" t="n">
@@ -18571,7 +18571,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:41.295</t>
+          <t>2026/6/30 00:37:41.295</t>
         </is>
       </c>
       <c r="C454" t="n">
@@ -18611,7 +18611,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:45.950</t>
+          <t>2026/6/30 00:37:45.950</t>
         </is>
       </c>
       <c r="C455" t="n">
@@ -18651,7 +18651,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:50.634</t>
+          <t>2026/6/30 00:37:50.634</t>
         </is>
       </c>
       <c r="C456" t="n">
@@ -18691,7 +18691,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:56.506</t>
+          <t>2026/6/30 00:37:56.506</t>
         </is>
       </c>
       <c r="C457" t="n">
@@ -18731,7 +18731,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:01.810</t>
+          <t>2026/6/30 00:38:01.810</t>
         </is>
       </c>
       <c r="C458" t="n">
@@ -18771,7 +18771,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:06.449</t>
+          <t>2026/6/30 00:38:06.449</t>
         </is>
       </c>
       <c r="C459" t="n">
@@ -18811,7 +18811,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:11.118</t>
+          <t>2026/6/30 00:38:11.118</t>
         </is>
       </c>
       <c r="C460" t="n">
@@ -18851,7 +18851,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:16.397</t>
+          <t>2026/6/30 00:38:16.397</t>
         </is>
       </c>
       <c r="C461" t="n">
@@ -18891,7 +18891,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:21.408</t>
+          <t>2026/6/30 00:38:21.408</t>
         </is>
       </c>
       <c r="C462" t="n">
@@ -18931,7 +18931,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:26.044</t>
+          <t>2026/6/30 00:38:26.044</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:30.735</t>
+          <t>2026/6/30 00:38:30.735</t>
         </is>
       </c>
       <c r="C464" t="n">
@@ -19011,7 +19011,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:36.000</t>
+          <t>2026/6/30 00:38:36.000</t>
         </is>
       </c>
       <c r="C465" t="n">
@@ -19051,7 +19051,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:40.956</t>
+          <t>2026/6/30 00:38:40.956</t>
         </is>
       </c>
       <c r="C466" t="n">
@@ -19091,7 +19091,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:45.667</t>
+          <t>2026/6/30 00:38:45.667</t>
         </is>
       </c>
       <c r="C467" t="n">
@@ -19131,7 +19131,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:50.299</t>
+          <t>2026/6/30 00:38:50.299</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -19171,7 +19171,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:56.179</t>
+          <t>2026/6/30 00:38:56.179</t>
         </is>
       </c>
       <c r="C469" t="n">
@@ -19211,7 +19211,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:00.868</t>
+          <t>2026/6/30 00:39:00.868</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -19251,7 +19251,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:05.526</t>
+          <t>2026/6/30 00:39:05.526</t>
         </is>
       </c>
       <c r="C471" t="n">
@@ -19291,7 +19291,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:10.178</t>
+          <t>2026/6/30 00:39:10.178</t>
         </is>
       </c>
       <c r="C472" t="n">
@@ -19331,7 +19331,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:15.470</t>
+          <t>2026/6/30 00:39:15.470</t>
         </is>
       </c>
       <c r="C473" t="n">
@@ -19371,7 +19371,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:20.460</t>
+          <t>2026/6/30 00:39:20.460</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -19411,7 +19411,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:25.087</t>
+          <t>2026/6/30 00:39:25.087</t>
         </is>
       </c>
       <c r="C475" t="n">
@@ -19451,7 +19451,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:29.769</t>
+          <t>2026/6/30 00:39:29.769</t>
         </is>
       </c>
       <c r="C476" t="n">
@@ -19491,7 +19491,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:35.060</t>
+          <t>2026/6/30 00:39:35.060</t>
         </is>
       </c>
       <c r="C477" t="n">
@@ -19531,7 +19531,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:40.010</t>
+          <t>2026/6/30 00:39:40.010</t>
         </is>
       </c>
       <c r="C478" t="n">
@@ -19571,7 +19571,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:44.710</t>
+          <t>2026/6/30 00:39:44.710</t>
         </is>
       </c>
       <c r="C479" t="n">
@@ -19611,7 +19611,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:49.342</t>
+          <t>2026/6/30 00:39:49.342</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -19651,7 +19651,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:54.939</t>
+          <t>2026/6/30 00:39:54.939</t>
         </is>
       </c>
       <c r="C481" t="n">
@@ -19691,7 +19691,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:59.907</t>
+          <t>2026/6/30 00:39:59.907</t>
         </is>
       </c>
       <c r="C482" t="n">
@@ -19731,7 +19731,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:04.605</t>
+          <t>2026/6/30 00:40:04.605</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -19771,7 +19771,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:09.253</t>
+          <t>2026/6/30 00:40:09.253</t>
         </is>
       </c>
       <c r="C484" t="n">
@@ -19811,7 +19811,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:14.245</t>
+          <t>2026/6/30 00:40:14.245</t>
         </is>
       </c>
       <c r="C485" t="n">
@@ -19851,7 +19851,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:19.175</t>
+          <t>2026/6/30 00:40:19.175</t>
         </is>
       </c>
       <c r="C486" t="n">
@@ -19891,7 +19891,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:23.868</t>
+          <t>2026/6/30 00:40:23.868</t>
         </is>
       </c>
       <c r="C487" t="n">
@@ -19931,7 +19931,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:33.513</t>
+          <t>2026/6/30 00:40:33.513</t>
         </is>
       </c>
       <c r="C488" t="n">
@@ -19971,7 +19971,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:38.762</t>
+          <t>2026/6/30 00:40:38.762</t>
         </is>
       </c>
       <c r="C489" t="n">
@@ -20011,7 +20011,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:43.436</t>
+          <t>2026/6/30 00:40:43.436</t>
         </is>
       </c>
       <c r="C490" t="n">
@@ -20051,7 +20051,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:48.085</t>
+          <t>2026/6/30 00:40:48.085</t>
         </is>
       </c>
       <c r="C491" t="n">
@@ -20091,7 +20091,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:53.100</t>
+          <t>2026/6/30 00:40:53.100</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -20131,7 +20131,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:58.691</t>
+          <t>2026/6/30 00:40:58.691</t>
         </is>
       </c>
       <c r="C493" t="n">
@@ -20171,7 +20171,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:03.364</t>
+          <t>2026/6/30 00:41:03.364</t>
         </is>
       </c>
       <c r="C494" t="n">
@@ -20211,7 +20211,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:07.981</t>
+          <t>2026/6/30 00:41:07.981</t>
         </is>
       </c>
       <c r="C495" t="n">
@@ -20251,7 +20251,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:12.664</t>
+          <t>2026/6/30 00:41:12.664</t>
         </is>
       </c>
       <c r="C496" t="n">
@@ -20291,7 +20291,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:17.323</t>
+          <t>2026/6/30 00:41:17.323</t>
         </is>
       </c>
       <c r="C497" t="n">
@@ -20331,7 +20331,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:21.979</t>
+          <t>2026/6/30 00:41:21.979</t>
         </is>
       </c>
       <c r="C498" t="n">
@@ -20371,7 +20371,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:26.623</t>
+          <t>2026/6/30 00:41:26.623</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -20411,7 +20411,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:31.334</t>
+          <t>2026/6/30 00:41:31.334</t>
         </is>
       </c>
       <c r="C500" t="n">
@@ -20451,7 +20451,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:35.971</t>
+          <t>2026/6/30 00:41:35.971</t>
         </is>
       </c>
       <c r="C501" t="n">
@@ -20491,7 +20491,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:40.627</t>
+          <t>2026/6/30 00:41:40.627</t>
         </is>
       </c>
       <c r="C502" t="n">
@@ -20531,7 +20531,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:45.279</t>
+          <t>2026/6/30 00:41:45.279</t>
         </is>
       </c>
       <c r="C503" t="n">
@@ -20571,7 +20571,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:49.990</t>
+          <t>2026/6/30 00:41:49.990</t>
         </is>
       </c>
       <c r="C504" t="n">
@@ -20611,7 +20611,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:54.623</t>
+          <t>2026/6/30 00:41:54.623</t>
         </is>
       </c>
       <c r="C505" t="n">
@@ -20651,7 +20651,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:59.278</t>
+          <t>2026/6/30 00:41:59.278</t>
         </is>
       </c>
       <c r="C506" t="n">
@@ -20691,7 +20691,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:03.941</t>
+          <t>2026/6/30 00:42:03.941</t>
         </is>
       </c>
       <c r="C507" t="n">
@@ -20731,7 +20731,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:13.294</t>
+          <t>2026/6/30 00:42:13.294</t>
         </is>
       </c>
       <c r="C508" t="n">
@@ -20771,7 +20771,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:17.911</t>
+          <t>2026/6/30 00:42:17.911</t>
         </is>
       </c>
       <c r="C509" t="n">
@@ -20811,7 +20811,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:22.612</t>
+          <t>2026/6/30 00:42:22.612</t>
         </is>
       </c>
       <c r="C510" t="n">
@@ -20851,7 +20851,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:27.279</t>
+          <t>2026/6/30 00:42:27.279</t>
         </is>
       </c>
       <c r="C511" t="n">
@@ -20891,7 +20891,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:31.933</t>
+          <t>2026/6/30 00:42:31.933</t>
         </is>
       </c>
       <c r="C512" t="n">
@@ -20931,7 +20931,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:36.586</t>
+          <t>2026/6/30 00:42:36.586</t>
         </is>
       </c>
       <c r="C513" t="n">
@@ -20971,7 +20971,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:41.275</t>
+          <t>2026/6/30 00:42:41.275</t>
         </is>
       </c>
       <c r="C514" t="n">
@@ -21011,7 +21011,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:45.900</t>
+          <t>2026/6/30 00:42:45.900</t>
         </is>
       </c>
       <c r="C515" t="n">
@@ -21051,7 +21051,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:50.579</t>
+          <t>2026/6/30 00:42:50.579</t>
         </is>
       </c>
       <c r="C516" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:55.262</t>
+          <t>2026/6/30 00:42:55.262</t>
         </is>
       </c>
       <c r="C517" t="n">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:59.893</t>
+          <t>2026/6/30 00:42:59.893</t>
         </is>
       </c>
       <c r="C518" t="n">
@@ -21171,7 +21171,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:04.589</t>
+          <t>2026/6/30 00:43:04.589</t>
         </is>
       </c>
       <c r="C519" t="n">
@@ -21211,7 +21211,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:09.201</t>
+          <t>2026/6/30 00:43:09.201</t>
         </is>
       </c>
       <c r="C520" t="n">
@@ -21251,7 +21251,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:13.891</t>
+          <t>2026/6/30 00:43:13.891</t>
         </is>
       </c>
       <c r="C521" t="n">
@@ -21291,7 +21291,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:23.223</t>
+          <t>2026/6/30 00:43:23.223</t>
         </is>
       </c>
       <c r="C522" t="n">
@@ -21331,7 +21331,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:27.919</t>
+          <t>2026/6/30 00:43:27.919</t>
         </is>
       </c>
       <c r="C523" t="n">
@@ -21371,7 +21371,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:32.531</t>
+          <t>2026/6/30 00:43:32.531</t>
         </is>
       </c>
       <c r="C524" t="n">
@@ -21411,7 +21411,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:37.199</t>
+          <t>2026/6/30 00:43:37.199</t>
         </is>
       </c>
       <c r="C525" t="n">
@@ -21451,7 +21451,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:41.900</t>
+          <t>2026/6/30 00:43:41.900</t>
         </is>
       </c>
       <c r="C526" t="n">
@@ -21491,7 +21491,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:46.539</t>
+          <t>2026/6/30 00:43:46.539</t>
         </is>
       </c>
       <c r="C527" t="n">
@@ -21531,7 +21531,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:51.199</t>
+          <t>2026/6/30 00:43:51.199</t>
         </is>
       </c>
       <c r="C528" t="n">
@@ -21571,7 +21571,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:55.832</t>
+          <t>2026/6/30 00:43:55.832</t>
         </is>
       </c>
       <c r="C529" t="n">
@@ -21611,7 +21611,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:00.512</t>
+          <t>2026/6/30 00:44:00.512</t>
         </is>
       </c>
       <c r="C530" t="n">
@@ -21651,7 +21651,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:05.170</t>
+          <t>2026/6/30 00:44:05.170</t>
         </is>
       </c>
       <c r="C531" t="n">
@@ -21691,7 +21691,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:09.837</t>
+          <t>2026/6/30 00:44:09.837</t>
         </is>
       </c>
       <c r="C532" t="n">
@@ -21731,7 +21731,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:14.513</t>
+          <t>2026/6/30 00:44:14.513</t>
         </is>
       </c>
       <c r="C533" t="n">
@@ -21771,7 +21771,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:19.160</t>
+          <t>2026/6/30 00:44:19.160</t>
         </is>
       </c>
       <c r="C534" t="n">
@@ -21811,7 +21811,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:28.493</t>
+          <t>2026/6/30 00:44:28.493</t>
         </is>
       </c>
       <c r="C535" t="n">
@@ -21851,7 +21851,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:33.176</t>
+          <t>2026/6/30 00:44:33.176</t>
         </is>
       </c>
       <c r="C536" t="n">
@@ -21891,7 +21891,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:37.811</t>
+          <t>2026/6/30 00:44:37.811</t>
         </is>
       </c>
       <c r="C537" t="n">
@@ -21931,7 +21931,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:42.491</t>
+          <t>2026/6/30 00:44:42.491</t>
         </is>
       </c>
       <c r="C538" t="n">
@@ -21971,7 +21971,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:47.146</t>
+          <t>2026/6/30 00:44:47.146</t>
         </is>
       </c>
       <c r="C539" t="n">
@@ -22011,7 +22011,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:51.805</t>
+          <t>2026/6/30 00:44:51.805</t>
         </is>
       </c>
       <c r="C540" t="n">
@@ -22051,7 +22051,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:56.449</t>
+          <t>2026/6/30 00:44:56.449</t>
         </is>
       </c>
       <c r="C541" t="n">
@@ -22091,7 +22091,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:01.137</t>
+          <t>2026/6/30 00:45:01.137</t>
         </is>
       </c>
       <c r="C542" t="n">
@@ -22131,7 +22131,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:05.816</t>
+          <t>2026/6/30 00:45:05.816</t>
         </is>
       </c>
       <c r="C543" t="n">
@@ -22171,7 +22171,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:10.469</t>
+          <t>2026/6/30 00:45:10.469</t>
         </is>
       </c>
       <c r="C544" t="n">
@@ -22211,7 +22211,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:15.142</t>
+          <t>2026/6/30 00:45:15.142</t>
         </is>
       </c>
       <c r="C545" t="n">
@@ -22251,7 +22251,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:19.765</t>
+          <t>2026/6/30 00:45:19.765</t>
         </is>
       </c>
       <c r="C546" t="n">
@@ -22291,7 +22291,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:24.482</t>
+          <t>2026/6/30 00:45:24.482</t>
         </is>
       </c>
       <c r="C547" t="n">
@@ -22331,7 +22331,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:29.121</t>
+          <t>2026/6/30 00:45:29.121</t>
         </is>
       </c>
       <c r="C548" t="n">
@@ -22371,7 +22371,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:38.425</t>
+          <t>2026/6/30 00:45:38.425</t>
         </is>
       </c>
       <c r="C549" t="n">
@@ -22411,7 +22411,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:43.129</t>
+          <t>2026/6/30 00:45:43.129</t>
         </is>
       </c>
       <c r="C550" t="n">
@@ -22451,7 +22451,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:47.741</t>
+          <t>2026/6/30 00:45:47.741</t>
         </is>
       </c>
       <c r="C551" t="n">
@@ -22491,7 +22491,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:52.421</t>
+          <t>2026/6/30 00:45:52.421</t>
         </is>
       </c>
       <c r="C552" t="n">
@@ -22531,7 +22531,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:57.119</t>
+          <t>2026/6/30 00:45:57.119</t>
         </is>
       </c>
       <c r="C553" t="n">
@@ -22571,7 +22571,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:01.730</t>
+          <t>2026/6/30 00:46:01.730</t>
         </is>
       </c>
       <c r="C554" t="n">
@@ -22611,7 +22611,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:06.428</t>
+          <t>2026/6/30 00:46:06.428</t>
         </is>
       </c>
       <c r="C555" t="n">
@@ -22651,7 +22651,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:11.049</t>
+          <t>2026/6/30 00:46:11.049</t>
         </is>
       </c>
       <c r="C556" t="n">
@@ -22691,7 +22691,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:15.717</t>
+          <t>2026/6/30 00:46:15.717</t>
         </is>
       </c>
       <c r="C557" t="n">
@@ -22731,7 +22731,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:20.380</t>
+          <t>2026/6/30 00:46:20.380</t>
         </is>
       </c>
       <c r="C558" t="n">
@@ -22771,7 +22771,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:25.025</t>
+          <t>2026/6/30 00:46:25.025</t>
         </is>
       </c>
       <c r="C559" t="n">
@@ -22811,7 +22811,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:29.731</t>
+          <t>2026/6/30 00:46:29.731</t>
         </is>
       </c>
       <c r="C560" t="n">
@@ -22851,7 +22851,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:34.370</t>
+          <t>2026/6/30 00:46:34.370</t>
         </is>
       </c>
       <c r="C561" t="n">
@@ -22891,7 +22891,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:39.029</t>
+          <t>2026/6/30 00:46:39.029</t>
         </is>
       </c>
       <c r="C562" t="n">
@@ -22931,7 +22931,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:48.397</t>
+          <t>2026/6/30 00:46:48.397</t>
         </is>
       </c>
       <c r="C563" t="n">
@@ -22971,7 +22971,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:53.041</t>
+          <t>2026/6/30 00:46:53.041</t>
         </is>
       </c>
       <c r="C564" t="n">
@@ -23011,7 +23011,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:57.686</t>
+          <t>2026/6/30 00:46:57.686</t>
         </is>
       </c>
       <c r="C565" t="n">
@@ -23051,7 +23051,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:02.374</t>
+          <t>2026/6/30 00:47:02.374</t>
         </is>
       </c>
       <c r="C566" t="n">
@@ -23091,7 +23091,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:07.009</t>
+          <t>2026/6/30 00:47:07.009</t>
         </is>
       </c>
       <c r="C567" t="n">
@@ -23131,7 +23131,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:11.700</t>
+          <t>2026/6/30 00:47:11.700</t>
         </is>
       </c>
       <c r="C568" t="n">
@@ -23171,7 +23171,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:16.331</t>
+          <t>2026/6/30 00:47:16.331</t>
         </is>
       </c>
       <c r="C569" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:21.013</t>
+          <t>2026/6/30 00:47:21.013</t>
         </is>
       </c>
       <c r="C570" t="n">
@@ -23251,7 +23251,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:25.671</t>
+          <t>2026/6/30 00:47:25.671</t>
         </is>
       </c>
       <c r="C571" t="n">
@@ -23291,7 +23291,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:30.321</t>
+          <t>2026/6/30 00:47:30.321</t>
         </is>
       </c>
       <c r="C572" t="n">
@@ -23331,7 +23331,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:35.022</t>
+          <t>2026/6/30 00:47:35.022</t>
         </is>
       </c>
       <c r="C573" t="n">
@@ -23371,7 +23371,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:39.643</t>
+          <t>2026/6/30 00:47:39.643</t>
         </is>
       </c>
       <c r="C574" t="n">
@@ -23411,7 +23411,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:44.314</t>
+          <t>2026/6/30 00:47:44.314</t>
         </is>
       </c>
       <c r="C575" t="n">
@@ -23451,7 +23451,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:49.004</t>
+          <t>2026/6/30 00:47:49.004</t>
         </is>
       </c>
       <c r="C576" t="n">
@@ -23491,7 +23491,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:58.331</t>
+          <t>2026/6/30 00:47:58.331</t>
         </is>
       </c>
       <c r="C577" t="n">
